--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdAssetInfo001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdAssetInfo001.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25330"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhouqiang\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9B46B0A-A4AE-4D3F-B86A-AF309830EA4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="21795" windowHeight="13245"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -51,16 +50,102 @@
     <t>穿透后混合类资产占总资产比例*</t>
   </si>
   <si>
-    <t>生效日（yyyy-mm-dd）*</t>
-  </si>
-  <si>
-    <t>生效截止日期（yyyy-mm-dd）*</t>
+    <r>
+      <t>生效日（yyyy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dd）*</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>生效截止日期（yyyy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dd）*</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -117,13 +202,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -429,19 +514,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="10.9296875" customWidth="1"/>
-    <col min="2" max="3" width="33.73046875" customWidth="1"/>
-    <col min="4" max="5" width="29.59765625" customWidth="1"/>
-    <col min="6" max="7" width="42.06640625" customWidth="1"/>
-    <col min="8" max="10" width="29.59765625" customWidth="1"/>
-    <col min="11" max="11" width="28.265625" customWidth="1"/>
+    <col min="1" max="1" width="10.875" customWidth="1"/>
+    <col min="2" max="3" width="33.75" customWidth="1"/>
+    <col min="4" max="5" width="29.625" customWidth="1"/>
+    <col min="6" max="7" width="42.125" customWidth="1"/>
+    <col min="8" max="10" width="29.625" customWidth="1"/>
+    <col min="11" max="11" width="28.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -469,17 +554,17 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="H2" s="3"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="H2" s="2"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -489,9 +574,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -500,9 +585,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdAssetInfo001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdAssetInfo001.xlsx
@@ -58,6 +58,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -68,6 +69,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -78,6 +80,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -88,6 +91,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -104,6 +108,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -114,6 +119,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -124,6 +130,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -134,6 +141,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -158,12 +166,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -198,17 +208,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -522,8 +535,9 @@
     <col min="2" max="3" width="33.75" customWidth="1"/>
     <col min="4" max="5" width="29.625" customWidth="1"/>
     <col min="6" max="7" width="42.125" customWidth="1"/>
-    <col min="8" max="10" width="29.625" customWidth="1"/>
-    <col min="11" max="11" width="28.25" customWidth="1"/>
+    <col min="8" max="9" width="29.625" customWidth="1"/>
+    <col min="10" max="10" width="29.625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="28.25" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.15">
@@ -554,17 +568,17 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="H2" s="2"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdAssetInfo001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdAssetInfo001.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\NYXP\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{687118A3-10C2-4609-9320-9C5DD00F8DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="21795" windowHeight="13245"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,30 +27,6 @@
     <t>产品主代码*</t>
   </si>
   <si>
-    <t>穿透前固定收益类资产占总资产比例*</t>
-  </si>
-  <si>
-    <t>穿透后固定收益类资产占总资产比例*</t>
-  </si>
-  <si>
-    <t>穿透前权益类资产占总资产比例*</t>
-  </si>
-  <si>
-    <t>穿透后权益类资产占总资产比例*</t>
-  </si>
-  <si>
-    <t>穿透前商品及金融衍生品类资产占总资产比例*</t>
-  </si>
-  <si>
-    <t>穿透后商品及金融衍生品类资产占总资产比例*</t>
-  </si>
-  <si>
-    <t>穿透前混合类资产占总资产比例*</t>
-  </si>
-  <si>
-    <t>穿透后混合类资产占总资产比例*</t>
-  </si>
-  <si>
     <r>
       <t>生效日（yyyy</t>
     </r>
@@ -147,13 +124,45 @@
       </rPr>
       <t>dd）*</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>穿透前固定收益类资产占总资产比例(%)*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>穿透后固定收益类资产占总资产比例(%)*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>穿透前权益类资产占总资产比例(%)*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>穿透后权益类资产占总资产比例(%)*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>穿透前商品及金融衍生品类资产占总资产比例(%)*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>穿透后商品及金融衍生品类资产占总资产比例(%)*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>穿透前混合类资产占总资产比例(%)*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>穿透后混合类资产占总资产比例(%)*</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -208,7 +217,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -222,6 +231,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -527,55 +539,56 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.875" customWidth="1"/>
-    <col min="2" max="3" width="33.75" customWidth="1"/>
-    <col min="4" max="5" width="29.625" customWidth="1"/>
-    <col min="6" max="7" width="42.125" customWidth="1"/>
-    <col min="8" max="9" width="29.625" customWidth="1"/>
-    <col min="10" max="10" width="29.625" style="4" customWidth="1"/>
-    <col min="11" max="11" width="28.25" style="4" customWidth="1"/>
+    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="38" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="49" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="35.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29.6640625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="28.21875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="K1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
-      </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H2" s="1"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
@@ -588,9 +601,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -599,9 +612,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
